--- a/backend/Blockchain/leader/alerts.xlsx
+++ b/backend/Blockchain/leader/alerts.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,46 +425,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Threat ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Source IP</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target IP</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Attack Count</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
@@ -2543,6 +2555,44 @@
         <v>1</v>
       </c>
       <c r="H56" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Session Hijacking</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>social enginnering</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>10.65.153.167</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-03T13:25:23</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>low</t>
         </is>

--- a/backend/Blockchain/leader/alerts.xlsx
+++ b/backend/Blockchain/leader/alerts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2598,6 +2598,82 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Keylogging</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>social enginnering</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>192.168.66.159</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-04T11:08:17</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Keylogging</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>social enginnering</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>192.168.66.159</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-04T11:08:17</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/Blockchain/leader/alerts.xlsx
+++ b/backend/Blockchain/leader/alerts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -481,36 +481,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>Cookie Stealing</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.148.64.251</t>
+          <t>192.168.186.159</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-29T10:23:43</t>
+          <t>2026-05-04T17:08:28</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -519,12 +519,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Keylogging</t>
+          <t>Brute Force</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>social enginnering</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -534,21 +534,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-29T10:27:25</t>
+          <t>2026-04-29T10:23:43</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Session Hijacking</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-29T10:29:45</t>
+          <t>2026-04-29T10:27:25</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,7 +586,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -605,12 +605,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>192.168.47.159</t>
+          <t>10.148.64.251</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-29T11:09:13</t>
+          <t>2026-04-29T10:29:45</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -624,7 +624,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-29T12:02:20</t>
+          <t>2026-04-29T11:09:13</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -662,7 +662,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -671,12 +671,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>XSS</t>
+          <t>Session Hijacking</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-29T12:02:11</t>
+          <t>2026-04-29T12:02:20</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -700,7 +700,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -709,12 +709,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Credential Harvesting</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-29T12:02:24</t>
+          <t>2026-04-29T12:02:11</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -738,7 +738,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cookie Stealing</t>
+          <t>Credential Harvesting</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-29T12:02:56</t>
+          <t>2026-04-29T12:02:24</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -776,7 +776,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -785,36 +785,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>Cookie Stealing</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>192.168.85.159</t>
+          <t>192.168.47.159</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-29T15:30:55</t>
+          <t>2026-04-29T12:02:56</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -852,45 +852,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brute Force</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>authentication</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>192.168.85.159</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>DoS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>192.168.85.159</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-29T15:55:07</t>
+          <t>2026-04-29T15:30:55</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>250</v>
+        <v>28</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -937,12 +937,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -952,21 +952,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-29T15:55:45</t>
+          <t>2026-04-29T15:55:07</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>245</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>critical</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -975,12 +975,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Session Hijacking</t>
+          <t>Brute Force</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>social enginnering</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -990,21 +990,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-29T16:13:39</t>
+          <t>2026-04-29T15:55:45</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1028,21 +1028,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-29T16:13:42</t>
+          <t>2026-04-29T16:13:39</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1066,30 +1066,30 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-30T22:13:45</t>
+          <t>2026-04-29T16:13:42</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>192.168.185.159</t>
+          <t>192.168.85.159</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Keylogging</t>
+          <t>Session Hijacking</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>192.168.185.159</t>
+          <t>192.168.85.159</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-29T21:41:14</t>
+          <t>2026-04-30T22:13:45</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1118,7 +1118,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-29T21:41:18</t>
+          <t>2026-04-29T21:41:14</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1156,31 +1156,31 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>192.168.29.124</t>
+          <t>192.168.185.159</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cookie Stealing</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>192.168.29.124</t>
+          <t>192.168.185.159</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-29T21:51:31</t>
+          <t>2026-04-29T21:41:18</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1194,45 +1194,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>127.0.0.1</t>
+          <t>192.168.29.124</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>Cookie Stealing</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10.148.64.251</t>
+          <t>192.168.29.124</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-29T22:00:30</t>
+          <t>2026-04-29T21:51:31</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1256,11 +1256,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-29T22:03:52</t>
+          <t>2026-04-29T22:00:30</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1270,11 +1270,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>192.168.29.124</t>
+          <t>127.0.0.1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1289,16 +1289,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>192.168.29.124</t>
+          <t>10.148.64.251</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-29T22:04:44</t>
+          <t>2026-04-29T22:03:52</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1308,45 +1308,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>127.0.0.1</t>
+          <t>192.168.29.124</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SQL Injection</t>
+          <t>Brute Force</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>webattack</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10.148.64.251</t>
+          <t>192.168.29.124</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-29T22:06:44</t>
+          <t>2026-04-29T22:04:44</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-29T22:07:10</t>
+          <t>2026-04-29T22:06:44</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1384,45 +1384,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>192.168.150.159</t>
+          <t>127.0.0.1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>SQL Injection</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>webattack</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>192.168.150.159</t>
+          <t>10.148.64.251</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-30T10:00:01</t>
+          <t>2026-04-29T22:07:10</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cookie Stealing</t>
+          <t>Brute Force</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1446,35 +1446,35 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-30T10:33:15</t>
+          <t>2026-04-30T10:00:01</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>127.0.0.1</t>
+          <t>192.168.150.159</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>XSS</t>
+          <t>Cookie Stealing</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-30T11:13:21</t>
+          <t>2026-04-30T10:33:15</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1498,7 +1498,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Keylogging</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>social enginnering</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-30T11:58:53</t>
+          <t>2026-04-30T11:13:21</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Credential Harvesting</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-30T12:06:36</t>
+          <t>2026-04-30T11:58:53</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1574,7 +1574,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1583,36 +1583,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>Credential Harvesting</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10.0.2.15</t>
+          <t>192.168.150.159</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-30T13:15:57</t>
+          <t>2026-04-30T12:06:36</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1636,11 +1636,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-30T13:16:11</t>
+          <t>2026-04-30T13:15:57</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1674,11 +1674,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-30T13:16:24</t>
+          <t>2026-04-30T13:16:11</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1750,21 +1750,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-30T13:16:35</t>
+          <t>2026-04-30T13:16:24</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Directory Traversal</t>
+          <t>Brute Force</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1788,21 +1788,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-30T13:18:52</t>
+          <t>2026-04-30T13:16:35</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1826,21 +1826,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-30T13:20:00</t>
+          <t>2026-04-30T13:18:52</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Credential Harvesting</t>
+          <t>Directory Traversal</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1859,26 +1859,26 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>192.168.53.159</t>
+          <t>10.0.2.15</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-01T12:43:22</t>
+          <t>2026-04-30T13:20:00</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>XSS</t>
+          <t>Credential Harvesting</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-01T12:43:27</t>
+          <t>2026-05-01T12:43:22</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1916,7 +1916,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Keylogging</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>social enginnering</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-01T12:43:53</t>
+          <t>2026-05-01T12:43:27</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -1954,7 +1954,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Credential Harvesting</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-01T12:44:32</t>
+          <t>2026-05-01T12:43:53</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -1992,7 +1992,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Keylogging</t>
+          <t>Credential Harvesting</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>social enginnering</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-01T12:44:28</t>
+          <t>2026-05-01T12:44:32</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2030,7 +2030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Session Hijacking</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2054,21 +2054,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-01T12:44:17</t>
+          <t>2026-05-01T12:44:28</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2077,36 +2077,36 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cookie Stealing</t>
+          <t>Session Hijacking</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>192.168.156.159</t>
+          <t>192.168.53.159</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-01T23:08:33</t>
+          <t>2026-05-01T12:44:17</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2115,36 +2115,36 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>Cookie Stealing</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>192.168.29.124</t>
+          <t>192.168.156.159</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-02T22:47:43</t>
+          <t>2026-05-01T23:08:33</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2168,11 +2168,11 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-02T22:47:54</t>
+          <t>2026-05-02T22:47:43</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2206,11 +2206,11 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-02T22:48:19</t>
+          <t>2026-05-02T22:47:54</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2229,12 +2229,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>XSS</t>
+          <t>Brute Force</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2244,21 +2244,21 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-02T22:50:22</t>
+          <t>2026-05-02T22:48:19</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-02T22:58:28</t>
+          <t>2026-05-02T22:50:22</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2320,11 +2320,11 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-02T22:58:31</t>
+          <t>2026-05-02T22:58:28</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2358,11 +2358,11 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-02T22:58:25</t>
+          <t>2026-05-02T22:58:31</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2396,11 +2396,11 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-02T22:58:28</t>
+          <t>2026-05-02T22:58:25</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2434,11 +2434,11 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-02T22:58:31</t>
+          <t>2026-05-02T22:58:28</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2448,45 +2448,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>192.168.29.124</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-02T22:58:31</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Keylogging</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>social enginnering</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-05-02T23:00:30</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Session Hijacking</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2510,21 +2510,21 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-02T23:00:56</t>
+          <t>2026-05-02T23:00:30</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2533,12 +2533,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Credential Harvesting</t>
+          <t>Session Hijacking</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2548,21 +2548,21 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-02T23:01:56</t>
+          <t>2026-05-02T23:00:56</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2571,22 +2571,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Session Hijacking</t>
+          <t>Credential Harvesting</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>social enginnering</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>10.65.153.167</t>
+          <t>192.168.29.124</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-03T13:25:23</t>
+          <t>2026-05-02T23:01:56</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2600,7 +2600,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2609,36 +2609,36 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Session Hijacking</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>192.168.29.124</t>
+          <t>10.65.153.167</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-03T21:56:38</t>
+          <t>2026-05-03T13:25:23</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2647,36 +2647,36 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>192.168.29.124</t>
+          <t>192.168.66.159</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-03T21:56:56</t>
+          <t>2026-05-04T11:08:17</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2685,598 +2685,28 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>192.168.29.124</t>
+          <t>192.168.66.159</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-03T22:04:29</t>
+          <t>2026-05-04T11:08:17</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H60" t="inlineStr">
-        <is>
-          <t>critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>DoS</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:08:38</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>160</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>DoS</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:08:41</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>40</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>DoS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-05-03T21:56:55</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>150</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>DoS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:08:38</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>176</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>DoS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-05-03T21:56:37</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>131</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>DoS</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:04:29</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>100</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Brute Force</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>authentication</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-05-03T13:50:12</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>23</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Brute Force</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>authentication</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:03:03</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>18</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Brute Force</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>authentication</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:07:16</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>25</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Cookie Stealing</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>data exfiltration</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-05-03T13:55:00</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>4</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Keylogging</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>social enginnering</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:01:36</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
-        <v>2</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Session Hijacking</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>social enginnering</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-05-03T13:53:29</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
-        <v>8</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-05-03T21:58:35</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
-        <v>2</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>57</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Keylogging</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>social enginnering</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>192.168.66.159</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-05-04T11:08:17</t>
-        </is>
-      </c>
-      <c r="G74" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>58</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Keylogging</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>social enginnering</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>192.168.66.159</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-05-04T11:08:17</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" t="inlineStr">
         <is>
           <t>low</t>
         </is>

--- a/backend/Blockchain/leader/alerts.xlsx
+++ b/backend/Blockchain/leader/alerts.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2712,6 +2712,44 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>192.168.26.159</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Brute Force</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>authentication</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>192.168.26.159</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-11T12:32:16</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>11</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/Blockchain/leader/alerts.xlsx
+++ b/backend/Blockchain/leader/alerts.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,46 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Threat ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Source IP</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Target IP</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Attack Count</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
@@ -472,7 +460,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -481,36 +469,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cookie Stealing</t>
+          <t>Brute Force</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>192.168.186.159</t>
+          <t>10.148.64.251</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-04T17:08:28</t>
+          <t>2026-04-29T10:23:43</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -519,12 +507,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -534,21 +522,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-29T10:23:43</t>
+          <t>2026-04-29T10:27:25</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -557,7 +545,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Keylogging</t>
+          <t>Session Hijacking</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -572,7 +560,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-29T10:27:25</t>
+          <t>2026-04-29T10:29:45</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,7 +574,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -605,12 +593,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.148.64.251</t>
+          <t>192.168.47.159</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-29T10:29:45</t>
+          <t>2026-04-29T11:09:13</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -624,7 +612,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -648,7 +636,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-29T11:09:13</t>
+          <t>2026-04-29T12:02:20</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -662,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -671,12 +659,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Session Hijacking</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>social enginnering</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -686,7 +674,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-29T12:02:20</t>
+          <t>2026-04-29T12:02:11</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -700,7 +688,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -709,12 +697,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>XSS</t>
+          <t>Credential Harvesting</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,7 +712,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-29T12:02:11</t>
+          <t>2026-04-29T12:02:24</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -738,7 +726,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -747,7 +735,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Credential Harvesting</t>
+          <t>Cookie Stealing</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -762,7 +750,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-29T12:02:24</t>
+          <t>2026-04-29T12:02:56</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -776,7 +764,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -785,36 +773,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cookie Stealing</t>
+          <t>Brute Force</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>192.168.47.159</t>
+          <t>192.168.85.159</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-29T12:02:56</t>
+          <t>2026-04-29T15:30:55</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -852,21 +840,21 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>127.0.0.1</t>
+          <t>192.168.85.159</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -876,21 +864,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-29T15:30:55</t>
+          <t>2026-04-29T15:55:07</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -918,7 +906,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -928,7 +916,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -937,12 +925,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Brute Force</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -952,21 +940,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-29T15:55:07</t>
+          <t>2026-04-29T15:55:45</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>245</v>
+        <v>5</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -975,12 +963,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>Session Hijacking</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -990,21 +978,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-29T15:55:45</t>
+          <t>2026-04-29T16:13:39</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1028,21 +1016,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-29T16:13:39</t>
+          <t>2026-04-29T16:13:42</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1066,30 +1054,30 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-29T16:13:42</t>
+          <t>2026-04-30T22:13:45</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>192.168.85.159</t>
+          <t>192.168.185.159</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Session Hijacking</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1099,12 +1087,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>192.168.85.159</t>
+          <t>192.168.185.159</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-30T22:13:45</t>
+          <t>2026-04-29T21:41:14</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1118,7 +1106,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1142,7 +1130,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-29T21:41:14</t>
+          <t>2026-04-29T21:41:18</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1156,31 +1144,31 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>192.168.185.159</t>
+          <t>192.168.29.124</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Keylogging</t>
+          <t>Cookie Stealing</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>social enginnering</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>192.168.185.159</t>
+          <t>192.168.29.124</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-29T21:41:18</t>
+          <t>2026-04-29T21:51:31</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1194,45 +1182,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brute Force</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>authentication</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>10.148.64.251</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-29T22:00:30</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Cookie Stealing</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>data exfiltration</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>192.168.29.124</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-29T21:51:31</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1256,11 +1244,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-29T22:00:30</t>
+          <t>2026-04-29T22:03:52</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1270,11 +1258,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>127.0.0.1</t>
+          <t>192.168.29.124</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1289,16 +1277,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10.148.64.251</t>
+          <t>192.168.29.124</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-29T22:03:52</t>
+          <t>2026-04-29T22:04:44</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1308,45 +1296,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>192.168.29.124</t>
+          <t>127.0.0.1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>SQL Injection</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>webattack</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>192.168.29.124</t>
+          <t>10.148.64.251</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-29T22:04:44</t>
+          <t>2026-04-29T22:06:44</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1370,7 +1358,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-29T22:06:44</t>
+          <t>2026-04-29T22:07:10</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1384,45 +1372,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>127.0.0.1</t>
+          <t>192.168.150.159</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SQL Injection</t>
+          <t>Brute Force</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>webattack</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.148.64.251</t>
+          <t>192.168.150.159</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-29T22:07:10</t>
+          <t>2026-04-30T10:00:01</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1431,12 +1419,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>Cookie Stealing</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1446,45 +1434,45 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-30T10:00:01</t>
+          <t>2026-04-30T10:33:15</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>XSS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>192.168.150.159</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Cookie Stealing</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>data exfiltration</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>192.168.150.159</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-30T10:33:15</t>
+          <t>2026-04-30T11:13:21</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1498,7 +1486,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1507,12 +1495,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>XSS</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1522,7 +1510,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-30T11:13:21</t>
+          <t>2026-04-30T11:58:53</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1536,7 +1524,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1545,12 +1533,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Keylogging</t>
+          <t>Credential Harvesting</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>social enginnering</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1560,7 +1548,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-30T11:58:53</t>
+          <t>2026-04-30T12:06:36</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1574,7 +1562,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1583,36 +1571,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Credential Harvesting</t>
+          <t>Brute Force</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>192.168.150.159</t>
+          <t>10.0.2.15</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-30T12:06:36</t>
+          <t>2026-04-30T13:15:57</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1636,11 +1624,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-30T13:15:57</t>
+          <t>2026-04-30T13:16:11</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1650,7 +1638,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1674,11 +1662,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-30T13:16:11</t>
+          <t>2026-04-30T13:16:24</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1688,7 +1676,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1716,7 +1704,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1726,7 +1714,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1750,21 +1738,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-30T13:16:24</t>
+          <t>2026-04-30T13:16:35</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1773,12 +1761,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>Directory Traversal</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1788,21 +1776,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-30T13:16:35</t>
+          <t>2026-04-30T13:18:52</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1826,21 +1814,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-30T13:18:52</t>
+          <t>2026-04-30T13:20:00</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1849,7 +1837,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Directory Traversal</t>
+          <t>Credential Harvesting</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1859,26 +1847,26 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>10.0.2.15</t>
+          <t>192.168.53.159</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-30T13:20:00</t>
+          <t>2026-05-01T12:43:22</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1887,12 +1875,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Credential Harvesting</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1902,7 +1890,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-01T12:43:22</t>
+          <t>2026-05-01T12:43:27</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1916,7 +1904,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1925,12 +1913,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>XSS</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1940,7 +1928,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-01T12:43:27</t>
+          <t>2026-05-01T12:43:53</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -1954,7 +1942,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1963,12 +1951,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Keylogging</t>
+          <t>Credential Harvesting</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>social enginnering</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1978,7 +1966,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-01T12:43:53</t>
+          <t>2026-05-01T12:44:32</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -1992,7 +1980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2001,12 +1989,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Credential Harvesting</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2016,7 +2004,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-01T12:44:32</t>
+          <t>2026-05-01T12:44:28</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2030,7 +2018,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2039,7 +2027,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Keylogging</t>
+          <t>Session Hijacking</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2054,21 +2042,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-01T12:44:28</t>
+          <t>2026-05-01T12:44:17</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2077,36 +2065,36 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Session Hijacking</t>
+          <t>Cookie Stealing</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>social enginnering</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>192.168.53.159</t>
+          <t>192.168.156.159</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-01T12:44:17</t>
+          <t>2026-05-01T23:08:33</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2115,36 +2103,36 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cookie Stealing</t>
+          <t>Brute Force</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>192.168.156.159</t>
+          <t>192.168.29.124</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-01T23:08:33</t>
+          <t>2026-05-02T22:47:43</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2168,11 +2156,11 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-02T22:47:43</t>
+          <t>2026-05-02T22:47:54</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2182,7 +2170,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2206,11 +2194,11 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-02T22:47:54</t>
+          <t>2026-05-02T22:48:19</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2220,7 +2208,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2229,12 +2217,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brute Force</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>authentication</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2244,21 +2232,21 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-02T22:48:19</t>
+          <t>2026-05-02T22:50:22</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2267,12 +2255,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>XSS</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2282,21 +2270,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-02T22:50:22</t>
+          <t>2026-05-02T22:58:28</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2320,11 +2308,11 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-02T22:58:28</t>
+          <t>2026-05-02T22:58:31</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2334,7 +2322,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2358,11 +2346,11 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-02T22:58:31</t>
+          <t>2026-05-02T22:58:25</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2372,7 +2360,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2396,11 +2384,11 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-02T22:58:25</t>
+          <t>2026-05-02T22:58:28</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2410,7 +2398,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2434,11 +2422,11 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-02T22:58:28</t>
+          <t>2026-05-02T22:58:31</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2448,7 +2436,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2457,12 +2445,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Keylogging</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2472,21 +2460,21 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-02T22:58:31</t>
+          <t>2026-05-02T23:00:30</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2495,7 +2483,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Keylogging</t>
+          <t>Session Hijacking</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2510,21 +2498,21 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-02T23:00:30</t>
+          <t>2026-05-02T23:00:56</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2533,12 +2521,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Session Hijacking</t>
+          <t>Credential Harvesting</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>social enginnering</t>
+          <t>data exfiltration</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2548,21 +2536,21 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-02T23:00:56</t>
+          <t>2026-05-02T23:01:56</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2571,22 +2559,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Credential Harvesting</t>
+          <t>Session Hijacking</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>data exfiltration</t>
+          <t>social enginnering</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>192.168.29.124</t>
+          <t>10.65.153.167</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-02T23:01:56</t>
+          <t>2026-05-03T13:25:23</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2595,158 +2583,6 @@
       <c r="H57" t="inlineStr">
         <is>
           <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Session Hijacking</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>social enginnering</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>10.65.153.167</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-05-03T13:25:23</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Keylogging</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>social enginnering</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>192.168.66.159</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-05-04T11:08:17</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Keylogging</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>social enginnering</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>192.168.66.159</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-05-04T11:08:17</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>192.168.26.159</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Brute Force</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>authentication</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>192.168.26.159</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-05-11T12:32:16</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>11</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>high</t>
         </is>
       </c>
     </row>
